--- a/AAII_Financials/Quarterly/ALZN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALZN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="92">
   <si>
     <t>ALZN</t>
   </si>
@@ -656,132 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43951</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43861</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43769</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -824,11 +831,11 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -866,8 +873,14 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -952,8 +965,14 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1038,8 +1057,14 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1095,102 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>400</v>
+      </c>
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1700</v>
-      </c>
-      <c r="T12" s="3">
-        <v>900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1800</v>
       </c>
       <c r="V12" s="3">
         <v>900</v>
       </c>
       <c r="W12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="X12" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y12" s="3">
         <v>300</v>
-      </c>
-      <c r="X12" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>800</v>
       </c>
       <c r="Z12" s="3">
         <v>200</v>
       </c>
       <c r="AA12" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC12" s="3">
         <v>400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>400</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1275,14 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1292,44 +1331,50 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1414,8 +1459,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1494,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1400</v>
       </c>
       <c r="J17" s="3">
         <v>1000</v>
       </c>
       <c r="K17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1900</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1400</v>
       </c>
       <c r="J18" s="3">
         <v>-1000</v>
       </c>
       <c r="K18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-3600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,8 +1712,10 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1691,11 +1758,11 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1727,68 +1794,74 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-3000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,8 +1892,14 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,114 +1964,126 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1400</v>
       </c>
       <c r="J23" s="3">
         <v>-1000</v>
       </c>
       <c r="K23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M23" s="3">
         <v>-900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2035,11 +2126,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -2077,8 +2168,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2260,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-1400</v>
       </c>
       <c r="J26" s="3">
         <v>-1000</v>
       </c>
       <c r="K26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2536,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2628,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2720,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,8 +2812,14 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2723,11 +2862,11 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -2759,100 +2898,112 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-1400</v>
       </c>
       <c r="J33" s="3">
         <v>-1000</v>
       </c>
       <c r="K33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3088,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-1400</v>
       </c>
       <c r="J35" s="3">
         <v>-1000</v>
       </c>
       <c r="K35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43951</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43861</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43769</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3315,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,82 +3349,84 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>700</v>
+      </c>
+      <c r="F41" s="3">
         <v>2700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>9200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>14100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>11800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>13600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>15600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1900</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>0</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
@@ -3264,8 +3437,14 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,8 +3529,14 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3397,11 +3582,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3421,11 +3606,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
@@ -3436,8 +3621,14 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3480,11 +3671,11 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3522,8 +3713,14 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3566,38 +3763,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3">
         <v>1200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>300</v>
       </c>
       <c r="T45" s="3">
         <v>600</v>
       </c>
       <c r="U45" s="3">
+        <v>300</v>
+      </c>
+      <c r="V45" s="3">
+        <v>600</v>
+      </c>
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1200</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="X45" s="3">
-        <v>700</v>
       </c>
       <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
+      <c r="Z45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>1000</v>
       </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
@@ -3608,83 +3805,89 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F46" s="3">
         <v>3700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>8400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>12100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>14400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>12400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>14500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>16800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,8 +3897,14 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3738,11 +3947,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3780,8 +3989,14 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3789,28 +4004,28 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>400</v>
       </c>
       <c r="H48" s="3">
+        <v>400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>400</v>
+      </c>
+      <c r="J48" s="3">
         <v>200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
       </c>
       <c r="L48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -3819,10 +4034,10 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>100</v>
@@ -3833,11 +4048,11 @@
       <c r="S48" s="3">
         <v>100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="T48" s="3">
+        <v>100</v>
+      </c>
+      <c r="U48" s="3">
+        <v>100</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3851,11 +4066,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -3866,8 +4081,14 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4173,14 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4265,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,8 +4357,14 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4168,11 +4407,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -4210,8 +4449,14 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,83 +4541,89 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F54" s="3">
         <v>4000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>8500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>10400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>12200</v>
-      </c>
-      <c r="S54" s="3">
-        <v>14500</v>
-      </c>
-      <c r="T54" s="3">
-        <v>12400</v>
       </c>
       <c r="U54" s="3">
         <v>14500</v>
       </c>
       <c r="V54" s="3">
+        <v>12400</v>
+      </c>
+      <c r="W54" s="3">
+        <v>14500</v>
+      </c>
+      <c r="X54" s="3">
         <v>16800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1000</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4633,14 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4671,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,83 +4705,85 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4793,14 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4559,14 +4826,14 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4589,25 +4856,25 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>300</v>
       </c>
       <c r="X58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y58" s="3">
         <v>300</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
+      <c r="Z58" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>300</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
@@ -4618,8 +4885,14 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4662,15 +4935,15 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
@@ -4678,22 +4951,22 @@
         <v>0</v>
       </c>
       <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
-      </c>
-      <c r="W59" s="3">
-        <v>100</v>
-      </c>
-      <c r="X59" s="3">
-        <v>900</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
+      <c r="Z59" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>100</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
@@ -4704,83 +4977,89 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1600</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +5069,14 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4876,8 +5161,14 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4905,15 +5196,15 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4926,11 +5217,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -4962,8 +5253,14 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5345,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5437,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,83 +5529,89 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1600</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5621,14 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5659,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5747,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5839,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5540,14 +5875,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>400</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5931,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,83 +6023,89 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-64400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-62200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-61200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-58500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-57400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-56400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-55000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-54000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-53200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-50500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-47600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-44100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-35300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-32200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-29200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-25300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-22800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-19200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-16800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +6115,14 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6207,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6299,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,83 +6391,89 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>700</v>
+      </c>
+      <c r="F76" s="3">
         <v>2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-1200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-2600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-4200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-2700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>8800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>11200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>12000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>13000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-700</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6483,14 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6575,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43951</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43861</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43769</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-1400</v>
       </c>
       <c r="J81" s="3">
         <v>-1000</v>
       </c>
       <c r="K81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6802,10 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6448,20 +6845,20 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -6475,11 +6872,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6493,8 +6890,14 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6982,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +7074,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +7166,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7258,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7350,106 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,8 +7480,10 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7055,41 +7496,41 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7127,8 +7568,14 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7660,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,8 +7752,14 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7313,80 +7772,86 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7882,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7461,11 +7928,11 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -7503,8 +7970,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +8062,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +8154,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,44 +8246,50 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>4000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>6300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -7808,47 +8299,53 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>3900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>14900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>3100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>800</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
       </c>
       <c r="AA100" s="3">
         <v>500</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1800</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7891,11 +8388,11 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -7933,90 +8430,102 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-2000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>13700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
